--- a/edufeedia_database_records.xlsx
+++ b/edufeedia_database_records.xlsx
@@ -501,7 +501,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>26c39428-5b45-4620-9117-da566aca126e</t>
+          <t>3ebc1dca-8bc0-4d04-9bfc-fadfd08b24c2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-09 09:55:32</t>
+          <t>2026-08-09 10:20:19</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>56794458-4e76-4e97-8048-4aa78b2a6da6</t>
+          <t>8cec8ce4-d88c-44b9-8b2b-b8a0ba2ca78c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -568,14 +568,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-09 09:55:33</t>
+          <t>2026-08-09 10:20:21</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>48dd72f2-78d7-4218-8eee-dbfed3124267</t>
+          <t>4a492680-2fff-4e7c-aa13-1a86cae1b2db</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -605,14 +605,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-09 09:55:33</t>
+          <t>2026-08-09 10:20:21</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cb120345-b521-49a1-8de3-a82365e93937</t>
+          <t>9f558171-714c-4b1d-bd54-d70fd74e39c1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -642,14 +642,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-09 09:55:33</t>
+          <t>2026-08-09 10:20:21</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4b284439-8cbe-4206-9e23-d199ca95e870</t>
+          <t>c02948a0-0078-4be9-9d27-70bc9de8d52c</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -679,14 +679,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-09 09:55:33</t>
+          <t>2026-08-09 10:20:21</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>b89b28b3-4945-4f55-bc05-5b96f508eb17</t>
+          <t>213a105d-ff71-4859-85d6-9dead107ca7c</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-09 09:55:34</t>
+          <t>2026-08-09 10:20:21</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>56794458-4e76-4e97-8048-4aa78b2a6da6</t>
+          <t>8cec8ce4-d88c-44b9-8b2b-b8a0ba2ca78c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>48dd72f2-78d7-4218-8eee-dbfed3124267</t>
+          <t>4a492680-2fff-4e7c-aa13-1a86cae1b2db</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -893,7 +893,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cb120345-b521-49a1-8de3-a82365e93937</t>
+          <t>9f558171-714c-4b1d-bd54-d70fd74e39c1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -939,7 +939,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4b284439-8cbe-4206-9e23-d199ca95e870</t>
+          <t>c02948a0-0078-4be9-9d27-70bc9de8d52c</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1069,7 +1069,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>169c2a77-6685-43f6-a0cb-ac9a7fa2465b</t>
+          <t>6086aa72-6443-4b04-b562-26a11d6b5270</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1116,7 +1116,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>05cc47d9-d807-46f0-9c2e-d9cf731d36dd</t>
+          <t>cdcafde9-1fd8-4544-b1c2-92fe93cfd5f9</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1163,7 +1163,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ffae7623-14c7-4ebe-a215-d1b18d77ead3</t>
+          <t>a3e5f1a8-ef4a-4281-a3ce-459ea0cf08a9</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1210,7 +1210,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>90c42a45-ae45-46c9-a67a-752c243dbc2a</t>
+          <t>618fa379-89eb-43f8-9d4d-ba2a4763b55e</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1257,7 +1257,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ca9bbd16-7732-4cc4-bb2f-84b3f564480c</t>
+          <t>3b912946-287e-440a-9bc7-47622145210b</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1304,7 +1304,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>284093e0-8aaa-436f-ba35-06e801c94552</t>
+          <t>ca623701-6773-4c2f-8e9e-15c630eb506c</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>91cbb526-018e-4dcc-b694-4d5986ea08fd</t>
+          <t>ddef0b48-90a6-4f7d-b224-b918346b8c4d</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1398,7 +1398,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>261f3d78-d691-4e12-9c51-de76e1e9ff46</t>
+          <t>9602123d-93d9-4ba4-8f22-6ca6c2440161</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1505,7 +1505,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>41f11065-c255-4acc-aaab-de0e08cc6b26</t>
+          <t>7d4e4ccd-489a-4570-a1e5-63875b8d0611</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1531,14 +1531,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-09 09:55:34</t>
+          <t>2026-08-09 10:20:21</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8339ab4c-9980-43a1-b110-c92b6e6a7df4</t>
+          <t>ad2c8717-0698-4bfc-955e-d4b4bc03d637</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-08 09:55:34</t>
+          <t>2026-08-08 10:20:21</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>fa9cada8-c7cb-47cb-b32d-b3e1b8e60239</t>
+          <t>6da38c7c-2c4d-47f2-8784-baba13dd1913</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1657,14 +1657,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-09 09:55:36</t>
+          <t>2026-08-09 10:20:23</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>a60beac0-2ffa-47f5-b101-addfc9887738</t>
+          <t>428e5853-3774-4a82-8296-a90cd2907e1c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1690,14 +1690,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-09 09:55:34</t>
+          <t>2026-08-09 10:20:21</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>e65cc4cf-e248-4f5f-88ae-e338fbd1e961</t>
+          <t>c8d9d555-05d1-448b-8565-3b75118b26e7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1723,14 +1723,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-09 09:55:34</t>
+          <t>2026-08-09 10:20:21</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00749191-addd-4542-8c36-d9800f21ab64</t>
+          <t>a5ea13f9-60fe-411e-bc5d-14e6958a0c63</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1756,14 +1756,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-09 09:55:34</t>
+          <t>2026-08-09 10:20:21</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>fbdcd22a-6932-4554-a8b1-d9585fa8cae8</t>
+          <t>44ce1411-6d37-44cd-84e8-028be2973884</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1789,14 +1789,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-09 09:55:34</t>
+          <t>2026-08-09 10:20:21</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>a1e392a3-553e-41ea-b1ac-85c593a84bc0</t>
+          <t>a634ac23-37db-423a-b5f9-c2962dc9bcfd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1822,14 +1822,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-09 09:55:34</t>
+          <t>2026-08-09 10:20:21</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ff1cfe42-f74f-4c67-bc43-dafa54ec4588</t>
+          <t>952ef3a3-6c0f-4da7-beab-8c6d12af6424</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1855,14 +1855,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-09 09:55:34</t>
+          <t>2026-08-09 10:20:21</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0a784836-fe4d-40f3-aa6d-e0fa134eb15b</t>
+          <t>f41e2dc3-8f30-475a-9968-85011b8492b3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1888,14 +1888,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-09 09:55:34</t>
+          <t>2026-08-09 10:20:21</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>956a8ef2-05ce-43ff-bbf9-6c7b8900b09d</t>
+          <t>7a58ec6d-7cfe-4e81-9064-4a0e03de3136</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1921,14 +1921,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-09 09:55:34</t>
+          <t>2026-08-09 10:20:21</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4cfde67c-9e23-49ef-952c-641d012ca79c</t>
+          <t>32924181-70d2-4cb8-a043-c2b6152d10cd</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1954,14 +1954,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-09 09:55:34</t>
+          <t>2026-08-09 10:20:21</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>64827ac8-f021-417a-b714-f1f45c2f4eb5</t>
+          <t>fe39a451-7cb4-4b0d-af9e-51b9fb45f0b9</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-08-09 09:55:34</t>
+          <t>2026-08-09 10:20:21</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2048,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>9bbc42ab-9bad-441b-8c44-fdbbd08a4475</t>
+          <t>493a2477-e8f9-4f7c-8c79-f4baf8390cdf</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2080,7 +2080,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>672d55f4-e818-4281-a4a8-8172958b8b87</t>
+          <t>d7188872-1a28-41eb-bace-15f1cc316912</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2113,7 +2113,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9bb4382e-7625-461b-83dd-d9c8102057cd</t>
+          <t>3397696f-c0e0-4876-9edb-06360463b259</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2145,7 +2145,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dabdb036-66a2-443d-958a-c4dddeafa6f2</t>
+          <t>09be49f2-8ed2-4c86-828a-d25febc097d2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2177,7 +2177,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>459ec6e5-6bea-44b3-bfd8-8aa16365fd74</t>
+          <t>64edae10-8ca7-4c10-b43b-47b7b2d5ee6c</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2210,7 +2210,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>e842825e-fbfa-4883-b7bf-a5565dfb1725</t>
+          <t>efcdfa0b-0541-4385-b92e-da0a829ebc46</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2243,7 +2243,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3df6f99d-afb6-4655-b1b6-cbc236cca311</t>
+          <t>8c44cd8a-ed1f-49ae-ae41-dec7a2e793a9</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2341,7 +2341,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ee748121-024e-474e-9b9a-a2db0091bacb</t>
+          <t>33c9ece0-c141-4c6a-84c3-b83a4791abb9</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2377,7 +2377,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>58f9b3f5-b67f-4399-b7ef-bc09fe5c6e2b</t>
+          <t>7d7bd9a5-e136-48fe-82e0-a0eda3c95150</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2473,7 +2473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>a60bd2b9-16e4-42fd-9583-e98460c579c8</t>
+          <t>3df29a8a-3508-47dd-869f-874c31b79078</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-09 09:55:34</t>
+          <t>2026-08-09 10:20:21</t>
         </is>
       </c>
     </row>

--- a/edufeedia_database_records.xlsx
+++ b/edufeedia_database_records.xlsx
@@ -501,7 +501,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3ebc1dca-8bc0-4d04-9bfc-fadfd08b24c2</t>
+          <t>75d02c53-339a-4ba9-ae31-76c22120a2e8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-09 10:20:19</t>
+          <t>2026-08-09 10:41:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8cec8ce4-d88c-44b9-8b2b-b8a0ba2ca78c</t>
+          <t>eaf34f04-daf2-45b9-b80d-050805fec610</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -568,14 +568,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-09 10:20:21</t>
+          <t>2026-08-09 10:41:02</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4a492680-2fff-4e7c-aa13-1a86cae1b2db</t>
+          <t>4523884e-5fd6-49bf-a7dd-43b06aece4fd</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -605,14 +605,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-09 10:20:21</t>
+          <t>2026-08-09 10:41:02</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9f558171-714c-4b1d-bd54-d70fd74e39c1</t>
+          <t>55b72682-82e6-4286-ba41-f4fdf8918a7f</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -642,14 +642,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-09 10:20:21</t>
+          <t>2026-08-09 10:41:02</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>c02948a0-0078-4be9-9d27-70bc9de8d52c</t>
+          <t>05b6cbbe-86b9-4ded-82ee-9aba19c4b15d</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -679,14 +679,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-09 10:20:21</t>
+          <t>2026-08-09 10:41:02</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>213a105d-ff71-4859-85d6-9dead107ca7c</t>
+          <t>42411dc7-7ecf-4731-8575-04c59822c034</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-09 10:20:21</t>
+          <t>2026-08-09 10:41:02</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8cec8ce4-d88c-44b9-8b2b-b8a0ba2ca78c</t>
+          <t>eaf34f04-daf2-45b9-b80d-050805fec610</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4a492680-2fff-4e7c-aa13-1a86cae1b2db</t>
+          <t>4523884e-5fd6-49bf-a7dd-43b06aece4fd</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -893,7 +893,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9f558171-714c-4b1d-bd54-d70fd74e39c1</t>
+          <t>55b72682-82e6-4286-ba41-f4fdf8918a7f</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -939,7 +939,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>c02948a0-0078-4be9-9d27-70bc9de8d52c</t>
+          <t>05b6cbbe-86b9-4ded-82ee-9aba19c4b15d</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1069,7 +1069,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6086aa72-6443-4b04-b562-26a11d6b5270</t>
+          <t>a0fd3513-ec70-4e7d-bc70-13239e037af6</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1116,7 +1116,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>cdcafde9-1fd8-4544-b1c2-92fe93cfd5f9</t>
+          <t>b999406b-1a85-467d-9ed6-3192b81989c7</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1163,7 +1163,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>a3e5f1a8-ef4a-4281-a3ce-459ea0cf08a9</t>
+          <t>a7c1d213-834e-43b6-9aa1-26f8c3c092ab</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1210,7 +1210,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>618fa379-89eb-43f8-9d4d-ba2a4763b55e</t>
+          <t>464925cb-f0ba-41a2-bcbf-d4b408bdd134</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1257,7 +1257,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3b912946-287e-440a-9bc7-47622145210b</t>
+          <t>b7384e16-f4a1-4164-815b-d50bc5062fe7</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1304,7 +1304,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ca623701-6773-4c2f-8e9e-15c630eb506c</t>
+          <t>55c57c86-730f-4b57-86dd-4803234f237e</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ddef0b48-90a6-4f7d-b224-b918346b8c4d</t>
+          <t>4937f8b9-bde6-4e48-95ec-a0ddc36dcd70</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1398,7 +1398,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>9602123d-93d9-4ba4-8f22-6ca6c2440161</t>
+          <t>3f9a53aa-f85c-4846-88d8-080a7fdc380a</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1505,7 +1505,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7d4e4ccd-489a-4570-a1e5-63875b8d0611</t>
+          <t>906b8ae2-b81e-44ce-abf4-c3325dbcc165</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1531,14 +1531,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-09 10:20:21</t>
+          <t>2026-08-09 10:41:02</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ad2c8717-0698-4bfc-955e-d4b4bc03d637</t>
+          <t>33b8ca3a-35b7-4205-8efb-e39316ce7ebf</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-08 10:20:21</t>
+          <t>2026-08-08 10:41:02</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -1631,7 +1631,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6da38c7c-2c4d-47f2-8784-baba13dd1913</t>
+          <t>97f2039c-446b-46a1-9efb-01a77d23d53f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1641,30 +1641,30 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Human Respiration Process Explained</t>
+          <t>Understanding Python Functions &amp; Scope</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>BOOKMARK</t>
+          <t>LIKE</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-09 10:20:23</t>
+          <t>2026-08-09 10:41:02</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>428e5853-3774-4a82-8296-a90cd2907e1c</t>
+          <t>9dac0925-ffa3-4802-a374-2ccbaf0055ab</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1674,30 +1674,30 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Understanding Python Functions &amp; Scope</t>
+          <t>Human Respiration Process Explained</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LIKE</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-09 10:20:21</t>
+          <t>2026-08-09 10:41:02</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>c8d9d555-05d1-448b-8565-3b75118b26e7</t>
+          <t>68bca430-3516-408a-bb46-96739746bcc4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Human Respiration Process Explained</t>
+          <t>Introduction to Quadratic Equations</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1723,47 +1723,47 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-09 10:20:21</t>
+          <t>2026-08-09 10:41:02</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>a5ea13f9-60fe-411e-bc5d-14e6958a0c63</t>
+          <t>a05caa6f-8ad6-4d78-8eaa-18af555f5b02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>rahul@apexschool.edu</t>
+          <t>aman@apexschool.edu</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Introduction to Quadratic Equations</t>
+          <t>Mysteries of Black Holes &amp; Event Horizons</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>LIKE</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-09 10:20:21</t>
+          <t>2026-08-09 10:41:02</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>44ce1411-6d37-44cd-84e8-028be2973884</t>
+          <t>f8b961db-5775-49f3-b16d-b6142865523c</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1773,30 +1773,30 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mysteries of Black Holes &amp; Event Horizons</t>
+          <t>Introduction to Artificial Intelligence &amp; Neural Networks</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LIKE</t>
+          <t>BOOKMARK</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-09 10:20:21</t>
+          <t>2026-08-09 10:41:02</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>a634ac23-37db-423a-b5f9-c2962dc9bcfd</t>
+          <t>bcaa843c-47af-4043-8f2f-8e1ee18784ed</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1806,63 +1806,63 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Introduction to Artificial Intelligence &amp; Neural Networks</t>
+          <t>Understanding Python Functions &amp; Scope</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BOOKMARK</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-09 10:20:21</t>
+          <t>2026-08-09 10:41:02</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>952ef3a3-6c0f-4da7-beab-8c6d12af6424</t>
+          <t>010d01a3-8522-4804-97d8-7c3e651c77a3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>aman@apexschool.edu</t>
+          <t>priya@apexschool.edu</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Understanding Python Functions &amp; Scope</t>
+          <t>Introduction to Artificial Intelligence &amp; Neural Networks</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-09 10:20:21</t>
+          <t>2026-08-09 10:41:02</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>f41e2dc3-8f30-475a-9968-85011b8492b3</t>
+          <t>b34e46cb-0db5-459d-9f13-6c6006b47b8d</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1872,30 +1872,30 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Introduction to Artificial Intelligence &amp; Neural Networks</t>
+          <t>Understanding Python Functions &amp; Scope</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VIEW</t>
+          <t>LIKE</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-09 10:20:21</t>
+          <t>2026-08-09 10:41:02</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>7a58ec6d-7cfe-4e81-9064-4a0e03de3136</t>
+          <t>c38f0d57-15a2-44db-a5e2-f2cea7c820c6</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1905,30 +1905,30 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Understanding Python Functions &amp; Scope</t>
+          <t>Arithmetic Progressions: nth Term &amp; Sum Formula</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LIKE</t>
+          <t>BOOKMARK</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-09 10:20:21</t>
+          <t>2026-08-09 10:41:02</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>32924181-70d2-4cb8-a043-c2b6152d10cd</t>
+          <t>379b2a77-7cf9-4bc4-b433-d35e029e0386</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1938,56 +1938,23 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Arithmetic Progressions: nth Term &amp; Sum Formula</t>
+          <t>Introduction to Quadratic Equations</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>BOOKMARK</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-09 10:20:21</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>fe39a451-7cb4-4b0d-af9e-51b9fb45f0b9</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>priya@apexschool.edu</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Introduction to Quadratic Equations</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>COMPLETED</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>5</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2026-08-09 10:20:21</t>
+          <t>2026-08-09 10:41:02</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2015,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>493a2477-e8f9-4f7c-8c79-f4baf8390cdf</t>
+          <t>a8935bd5-6ad6-43b0-81ac-583c1d72f66a</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2080,7 +2047,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>d7188872-1a28-41eb-bace-15f1cc316912</t>
+          <t>fcbb60b8-a579-4c6a-b28d-f84ee70d1cd7</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2113,7 +2080,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3397696f-c0e0-4876-9edb-06360463b259</t>
+          <t>0f7cd117-ab35-48d7-870a-e924128ecb82</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2145,7 +2112,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09be49f2-8ed2-4c86-828a-d25febc097d2</t>
+          <t>d337c4e7-3395-4224-8f67-14f051326602</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2177,7 +2144,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>64edae10-8ca7-4c10-b43b-47b7b2d5ee6c</t>
+          <t>298f0912-d458-4495-a5b3-f5a02023b707</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2210,7 +2177,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>efcdfa0b-0541-4385-b92e-da0a829ebc46</t>
+          <t>9a49f092-40a4-4523-825e-0d9c7f786b1a</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2243,7 +2210,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8c44cd8a-ed1f-49ae-ae41-dec7a2e793a9</t>
+          <t>b459df1b-8d88-4a16-9c38-026e4c45573a</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2341,7 +2308,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>33c9ece0-c141-4c6a-84c3-b83a4791abb9</t>
+          <t>56fca263-5faa-44eb-a98e-caf8295012c9</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2377,7 +2344,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>7d7bd9a5-e136-48fe-82e0-a0eda3c95150</t>
+          <t>d1cd767a-fb77-4808-8bed-0f74e9778598</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2473,7 +2440,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3df29a8a-3508-47dd-869f-874c31b79078</t>
+          <t>dbd30707-9467-414b-8a6d-d774842b7bfa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2503,7 +2470,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-09 10:20:21</t>
+          <t>2026-08-09 10:41:02</t>
         </is>
       </c>
     </row>

--- a/edufeedia_database_records.xlsx
+++ b/edufeedia_database_records.xlsx
@@ -501,7 +501,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>75d02c53-339a-4ba9-ae31-76c22120a2e8</t>
+          <t>27ef40fe-5e1a-4607-97db-30141c1c5cec</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-09 10:41:00</t>
+          <t>2026-08-09 10:50:19</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>eaf34f04-daf2-45b9-b80d-050805fec610</t>
+          <t>2d48608b-f78e-479e-a796-7f65c52540bc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -568,14 +568,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-09 10:41:02</t>
+          <t>2026-08-09 10:50:21</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4523884e-5fd6-49bf-a7dd-43b06aece4fd</t>
+          <t>1b2a6f68-3d51-499a-a05b-ed72da7fa164</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -605,14 +605,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-09 10:41:02</t>
+          <t>2026-08-09 10:50:21</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>55b72682-82e6-4286-ba41-f4fdf8918a7f</t>
+          <t>0c068795-d2e7-45e3-820b-4c1641b3d351</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -642,14 +642,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-09 10:41:02</t>
+          <t>2026-08-09 10:50:21</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>05b6cbbe-86b9-4ded-82ee-9aba19c4b15d</t>
+          <t>ad9f4587-02b7-47fa-8ab9-8affd8ddf62e</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -679,14 +679,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-09 10:41:02</t>
+          <t>2026-08-09 10:50:21</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>42411dc7-7ecf-4731-8575-04c59822c034</t>
+          <t>0b2929f4-3c8b-4e02-bfd7-646494bd897c</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-09 10:41:02</t>
+          <t>2026-08-09 10:50:21</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>eaf34f04-daf2-45b9-b80d-050805fec610</t>
+          <t>2d48608b-f78e-479e-a796-7f65c52540bc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4523884e-5fd6-49bf-a7dd-43b06aece4fd</t>
+          <t>1b2a6f68-3d51-499a-a05b-ed72da7fa164</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -893,7 +893,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>55b72682-82e6-4286-ba41-f4fdf8918a7f</t>
+          <t>0c068795-d2e7-45e3-820b-4c1641b3d351</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -939,7 +939,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>05b6cbbe-86b9-4ded-82ee-9aba19c4b15d</t>
+          <t>ad9f4587-02b7-47fa-8ab9-8affd8ddf62e</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1069,7 +1069,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>a0fd3513-ec70-4e7d-bc70-13239e037af6</t>
+          <t>7a65f97f-c56e-40aa-962a-6a4334d96e05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1116,7 +1116,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>b999406b-1a85-467d-9ed6-3192b81989c7</t>
+          <t>12c1c19e-7e4b-4662-8580-5bf8d201b6c8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1163,7 +1163,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>a7c1d213-834e-43b6-9aa1-26f8c3c092ab</t>
+          <t>236ffa36-c166-4793-ac98-ea4ff7490ea3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1210,7 +1210,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>464925cb-f0ba-41a2-bcbf-d4b408bdd134</t>
+          <t>20427fba-9d64-46b6-be8b-4411b54cf118</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1257,7 +1257,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>b7384e16-f4a1-4164-815b-d50bc5062fe7</t>
+          <t>c2165665-4afe-492a-88b6-a679dd53e41a</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1304,7 +1304,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>55c57c86-730f-4b57-86dd-4803234f237e</t>
+          <t>c79e4df4-f5a4-4fbe-b47f-472d0a91119a</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4937f8b9-bde6-4e48-95ec-a0ddc36dcd70</t>
+          <t>d2b2d95b-dd6d-4b74-a267-fabd48415ddf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1398,7 +1398,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3f9a53aa-f85c-4846-88d8-080a7fdc380a</t>
+          <t>8b4344d9-f685-4203-9144-b7e0dd302deb</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1505,7 +1505,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>906b8ae2-b81e-44ce-abf4-c3325dbcc165</t>
+          <t>5bf12a41-c9ff-4185-bf00-274a7485e8e0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1531,14 +1531,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-09 10:41:02</t>
+          <t>2026-08-09 10:50:21</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>33b8ca3a-35b7-4205-8efb-e39316ce7ebf</t>
+          <t>5e030848-ad47-479a-bf7b-f4cbb07e24af</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-08 10:41:02</t>
+          <t>2026-08-08 10:50:21</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>97f2039c-446b-46a1-9efb-01a77d23d53f</t>
+          <t>622c5111-5a70-4ca9-9ca3-8bacd7426403</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1657,14 +1657,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-09 10:41:02</t>
+          <t>2026-08-09 10:50:21</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9dac0925-ffa3-4802-a374-2ccbaf0055ab</t>
+          <t>9dd1d7b4-047b-4b70-a8d3-8685f5b22e44</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1690,14 +1690,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-09 10:41:02</t>
+          <t>2026-08-09 10:50:21</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>68bca430-3516-408a-bb46-96739746bcc4</t>
+          <t>6ab21b36-f77d-4497-b395-865069f60ebe</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1723,14 +1723,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-09 10:41:02</t>
+          <t>2026-08-09 10:50:21</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>a05caa6f-8ad6-4d78-8eaa-18af555f5b02</t>
+          <t>b6309afc-a435-4503-802a-6e3ff69878ae</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1756,14 +1756,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-09 10:41:02</t>
+          <t>2026-08-09 10:50:21</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>f8b961db-5775-49f3-b16d-b6142865523c</t>
+          <t>56d73176-ef05-4c0a-b5b6-20c18a980d6f</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1789,14 +1789,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-09 10:41:02</t>
+          <t>2026-08-09 10:50:21</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bcaa843c-47af-4043-8f2f-8e1ee18784ed</t>
+          <t>3d7bc204-cdb5-4d20-a83d-f635cd9d90f7</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1822,14 +1822,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-09 10:41:02</t>
+          <t>2026-08-09 10:50:21</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>010d01a3-8522-4804-97d8-7c3e651c77a3</t>
+          <t>93881e74-a69c-4686-b6ea-ca6c77eb8464</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1855,14 +1855,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-09 10:41:02</t>
+          <t>2026-08-09 10:50:21</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>b34e46cb-0db5-459d-9f13-6c6006b47b8d</t>
+          <t>35dd084d-5372-432a-ae23-549483166722</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1888,14 +1888,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-09 10:41:02</t>
+          <t>2026-08-09 10:50:21</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>c38f0d57-15a2-44db-a5e2-f2cea7c820c6</t>
+          <t>59873d8c-f0da-4df8-8b8c-221cce6fabfb</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1921,14 +1921,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-09 10:41:02</t>
+          <t>2026-08-09 10:50:21</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>379b2a77-7cf9-4bc4-b433-d35e029e0386</t>
+          <t>765771fc-5cb4-4344-ba11-000d9636a0af</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-09 10:41:02</t>
+          <t>2026-08-09 10:50:21</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>a8935bd5-6ad6-43b0-81ac-583c1d72f66a</t>
+          <t>3855b1a1-81b6-4eff-a59c-aa3e7ec28944</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2047,7 +2047,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>fcbb60b8-a579-4c6a-b28d-f84ee70d1cd7</t>
+          <t>eaaad540-cb4e-4eb5-a728-97b01f6df9b4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2080,7 +2080,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0f7cd117-ab35-48d7-870a-e924128ecb82</t>
+          <t>a77dec7b-44cf-4f81-b99b-f0d252ccc52f</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2112,7 +2112,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>d337c4e7-3395-4224-8f67-14f051326602</t>
+          <t>9ba05b93-42d0-467c-9ebb-2c9df7b467f9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2144,7 +2144,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>298f0912-d458-4495-a5b3-f5a02023b707</t>
+          <t>804f2f7a-173c-41a8-bf1d-46645efc69d5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2177,7 +2177,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9a49f092-40a4-4523-825e-0d9c7f786b1a</t>
+          <t>f28f0a78-d1b5-4fb7-bde3-764c8c8960f6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2210,7 +2210,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>b459df1b-8d88-4a16-9c38-026e4c45573a</t>
+          <t>a4bb3ae5-b1e8-4ae1-816f-4153862fce3e</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2308,7 +2308,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>56fca263-5faa-44eb-a98e-caf8295012c9</t>
+          <t>afa323d3-4e48-4246-ae71-4a5c17182eda</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2344,7 +2344,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>d1cd767a-fb77-4808-8bed-0f74e9778598</t>
+          <t>42e916f8-e5e8-4716-9a58-0e5d39d7f707</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2440,7 +2440,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>dbd30707-9467-414b-8a6d-d774842b7bfa</t>
+          <t>9458bf7f-693c-4eb8-84b3-390a28581893</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-09 10:41:02</t>
+          <t>2026-08-09 10:50:21</t>
         </is>
       </c>
     </row>

--- a/edufeedia_database_records.xlsx
+++ b/edufeedia_database_records.xlsx
@@ -501,7 +501,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>27ef40fe-5e1a-4607-97db-30141c1c5cec</t>
+          <t>7ce5668e-83d9-49ef-b960-213ad52f3037</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-09 10:50:19</t>
+          <t>2026-08-09 10:59:28</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2d48608b-f78e-479e-a796-7f65c52540bc</t>
+          <t>726c3401-6186-492a-bcc8-0b71432b99cd</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -568,14 +568,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-09 10:50:21</t>
+          <t>2026-08-09 10:59:30</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1b2a6f68-3d51-499a-a05b-ed72da7fa164</t>
+          <t>f70a76fc-46ed-4d6d-af60-e55ff79d976c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -605,14 +605,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-09 10:50:21</t>
+          <t>2026-08-09 10:59:30</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0c068795-d2e7-45e3-820b-4c1641b3d351</t>
+          <t>67291ef5-7932-494a-a5ad-ea8ee894819d</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -642,14 +642,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-09 10:50:21</t>
+          <t>2026-08-09 10:59:30</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ad9f4587-02b7-47fa-8ab9-8affd8ddf62e</t>
+          <t>325043fb-6bec-4295-98c6-22e9e7559352</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -679,14 +679,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-09 10:50:21</t>
+          <t>2026-08-09 10:59:30</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0b2929f4-3c8b-4e02-bfd7-646494bd897c</t>
+          <t>1f494347-4c10-4753-b6d3-83d9e3a8f2d8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-09 10:50:21</t>
+          <t>2026-08-09 10:59:30</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2d48608b-f78e-479e-a796-7f65c52540bc</t>
+          <t>726c3401-6186-492a-bcc8-0b71432b99cd</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1b2a6f68-3d51-499a-a05b-ed72da7fa164</t>
+          <t>f70a76fc-46ed-4d6d-af60-e55ff79d976c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -893,7 +893,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0c068795-d2e7-45e3-820b-4c1641b3d351</t>
+          <t>67291ef5-7932-494a-a5ad-ea8ee894819d</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -939,7 +939,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ad9f4587-02b7-47fa-8ab9-8affd8ddf62e</t>
+          <t>325043fb-6bec-4295-98c6-22e9e7559352</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1069,7 +1069,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7a65f97f-c56e-40aa-962a-6a4334d96e05</t>
+          <t>42a58560-9281-4d6b-a620-cf5960faee91</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1116,7 +1116,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>12c1c19e-7e4b-4662-8580-5bf8d201b6c8</t>
+          <t>3525d5ac-2903-44b3-9e6d-9175f626f2bb</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I3" t="n">
         <v>96</v>
@@ -1163,7 +1163,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>236ffa36-c166-4793-ac98-ea4ff7490ea3</t>
+          <t>91efcd4b-44ac-42ae-970b-3a13d0524ea0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1210,7 +1210,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20427fba-9d64-46b6-be8b-4411b54cf118</t>
+          <t>5c66bbba-eea9-4cfb-b61c-79ea2bf5b21d</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1257,7 +1257,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>c2165665-4afe-492a-88b6-a679dd53e41a</t>
+          <t>ea3dc646-aa67-4393-bb33-50a65c5c3cae</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I6" t="n">
         <v>94</v>
@@ -1304,7 +1304,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>c79e4df4-f5a4-4fbe-b47f-472d0a91119a</t>
+          <t>3996ba82-ef06-4fe6-acb1-bfbce8fdd71a</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I7" t="n">
         <v>99</v>
@@ -1351,7 +1351,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>d2b2d95b-dd6d-4b74-a267-fabd48415ddf</t>
+          <t>d6c7d568-8465-4a05-ba87-58caa246cbc1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I8" t="n">
         <v>98</v>
@@ -1398,7 +1398,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8b4344d9-f685-4203-9144-b7e0dd302deb</t>
+          <t>fdf8c65c-11b0-4fcf-b0fd-621d5de4dd1b</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I9" t="n">
         <v>96</v>
@@ -1505,7 +1505,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5bf12a41-c9ff-4185-bf00-274a7485e8e0</t>
+          <t>c016901d-6f8b-4d51-998f-eeacff3b7301</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1531,14 +1531,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-09 10:50:21</t>
+          <t>2026-08-09 10:59:30</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5e030848-ad47-479a-bf7b-f4cbb07e24af</t>
+          <t>04719a7d-c411-4604-9577-c7410165aab0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-08 10:50:21</t>
+          <t>2026-08-08 10:59:30</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -1631,7 +1631,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>622c5111-5a70-4ca9-9ca3-8bacd7426403</t>
+          <t>afa17b87-234f-4ec9-9438-45eeb63f1673</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1641,30 +1641,30 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Understanding Python Functions &amp; Scope</t>
+          <t>Human Respiration Process Explained</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LIKE</t>
+          <t>BOOKMARK</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-09 10:50:21</t>
+          <t>2026-08-09 10:59:32</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9dd1d7b4-047b-4b70-a8d3-8685f5b22e44</t>
+          <t>e05fb65b-8b92-45fb-ad77-7298d65b7dab</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1674,30 +1674,30 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Human Respiration Process Explained</t>
+          <t>Understanding Python Functions &amp; Scope</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>LIKE</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-09 10:50:21</t>
+          <t>2026-08-09 10:59:30</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6ab21b36-f77d-4497-b395-865069f60ebe</t>
+          <t>575d97b0-2f02-494e-9211-70ecb9b4ac19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Introduction to Quadratic Equations</t>
+          <t>Human Respiration Process Explained</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1723,47 +1723,47 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-09 10:50:21</t>
+          <t>2026-08-09 10:59:30</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>b6309afc-a435-4503-802a-6e3ff69878ae</t>
+          <t>d4fec113-500d-48f7-9698-37fc15a10d14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>aman@apexschool.edu</t>
+          <t>rahul@apexschool.edu</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mysteries of Black Holes &amp; Event Horizons</t>
+          <t>Introduction to Quadratic Equations</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LIKE</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-09 10:50:21</t>
+          <t>2026-08-09 10:59:30</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>56d73176-ef05-4c0a-b5b6-20c18a980d6f</t>
+          <t>e72b45c6-e1f4-46be-a202-20bf8af72c6d</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1773,30 +1773,30 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Introduction to Artificial Intelligence &amp; Neural Networks</t>
+          <t>Mysteries of Black Holes &amp; Event Horizons</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>BOOKMARK</t>
+          <t>LIKE</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-09 10:50:21</t>
+          <t>2026-08-09 10:59:30</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3d7bc204-cdb5-4d20-a83d-f635cd9d90f7</t>
+          <t>e200b324-a1d3-4fa0-bec8-1721248b01b0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1806,63 +1806,63 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Understanding Python Functions &amp; Scope</t>
+          <t>Introduction to Artificial Intelligence &amp; Neural Networks</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>BOOKMARK</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-09 10:50:21</t>
+          <t>2026-08-09 10:59:30</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>93881e74-a69c-4686-b6ea-ca6c77eb8464</t>
+          <t>be6cccf2-4ca6-4053-b3d4-95a10c91b426</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>priya@apexschool.edu</t>
+          <t>aman@apexschool.edu</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Introduction to Artificial Intelligence &amp; Neural Networks</t>
+          <t>Understanding Python Functions &amp; Scope</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VIEW</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-09 10:50:21</t>
+          <t>2026-08-09 10:59:30</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>35dd084d-5372-432a-ae23-549483166722</t>
+          <t>3428dada-ec75-4021-8277-06dad01422b6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1872,30 +1872,30 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Understanding Python Functions &amp; Scope</t>
+          <t>Introduction to Artificial Intelligence &amp; Neural Networks</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LIKE</t>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-09 10:50:21</t>
+          <t>2026-08-09 10:59:30</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>59873d8c-f0da-4df8-8b8c-221cce6fabfb</t>
+          <t>6ac26069-87a8-43f5-a411-2ccd1c4d73fe</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1905,30 +1905,30 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Arithmetic Progressions: nth Term &amp; Sum Formula</t>
+          <t>Understanding Python Functions &amp; Scope</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BOOKMARK</t>
+          <t>LIKE</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-09 10:50:21</t>
+          <t>2026-08-09 10:59:30</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>765771fc-5cb4-4344-ba11-000d9636a0af</t>
+          <t>c73e3b39-c516-49e0-b2f9-fd48f4ed1aad</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1938,23 +1938,56 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Introduction to Quadratic Equations</t>
+          <t>Arithmetic Progressions: nth Term &amp; Sum Formula</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>BOOKMARK</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-09 10:50:21</t>
+          <t>2026-08-09 10:59:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>b471ca3e-ddfe-4087-9eb9-88ffe7076ccf</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>priya@apexschool.edu</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Introduction to Quadratic Equations</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-08-09 10:59:30</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2048,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3855b1a1-81b6-4eff-a59c-aa3e7ec28944</t>
+          <t>b56da297-d12b-4a48-88c6-0b901580fdb8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2047,7 +2080,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>eaaad540-cb4e-4eb5-a728-97b01f6df9b4</t>
+          <t>fe49f774-d442-4b23-8d91-0b0787150553</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2080,7 +2113,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>a77dec7b-44cf-4f81-b99b-f0d252ccc52f</t>
+          <t>3cf8ed84-cd4a-48c0-b02f-36861b514214</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2112,7 +2145,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9ba05b93-42d0-467c-9ebb-2c9df7b467f9</t>
+          <t>17ec79f0-20ae-4171-b5b5-8c715a64916c</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2144,7 +2177,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>804f2f7a-173c-41a8-bf1d-46645efc69d5</t>
+          <t>e746dbac-a6cf-45a5-9d3b-9495389b55e5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2177,7 +2210,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>f28f0a78-d1b5-4fb7-bde3-764c8c8960f6</t>
+          <t>128e867e-8871-4205-80fd-09f89c27e8da</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2210,7 +2243,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>a4bb3ae5-b1e8-4ae1-816f-4153862fce3e</t>
+          <t>b835b6b9-e51b-422c-a734-0d56ac44b4c7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2308,7 +2341,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>afa323d3-4e48-4246-ae71-4a5c17182eda</t>
+          <t>34717c3d-e914-43fe-a6d9-375f5b5d44a4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2344,7 +2377,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>42e916f8-e5e8-4716-9a58-0e5d39d7f707</t>
+          <t>37beccf3-d8ab-429e-a5f7-df6fd048c9f6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2440,7 +2473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>9458bf7f-693c-4eb8-84b3-390a28581893</t>
+          <t>5ff8ee9a-98bb-449d-ac77-1427d6c4721e</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2470,7 +2503,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-09 10:50:21</t>
+          <t>2026-08-09 10:59:30</t>
         </is>
       </c>
     </row>

--- a/edufeedia_database_records.xlsx
+++ b/edufeedia_database_records.xlsx
@@ -501,7 +501,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7ce5668e-83d9-49ef-b960-213ad52f3037</t>
+          <t>a6f7ba00-78db-48eb-b5b1-38cd17d66f41</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-09 10:59:28</t>
+          <t>2026-08-09 11:07:32</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>726c3401-6186-492a-bcc8-0b71432b99cd</t>
+          <t>0a421413-31a7-403c-a3db-0e8a74189a00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -568,14 +568,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-09 10:59:30</t>
+          <t>2026-08-09 11:07:34</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>f70a76fc-46ed-4d6d-af60-e55ff79d976c</t>
+          <t>4e0a2487-0009-4c74-b6a7-9c4bda02f031</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -605,14 +605,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-09 10:59:30</t>
+          <t>2026-08-09 11:07:34</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>67291ef5-7932-494a-a5ad-ea8ee894819d</t>
+          <t>bf44b90a-798f-45c7-8da0-077853bae445</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -642,14 +642,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-09 10:59:30</t>
+          <t>2026-08-09 11:07:34</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>325043fb-6bec-4295-98c6-22e9e7559352</t>
+          <t>6afbb9d3-c2d4-4734-b29a-e19e2c7ec654</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -679,14 +679,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-09 10:59:30</t>
+          <t>2026-08-09 11:07:34</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1f494347-4c10-4753-b6d3-83d9e3a8f2d8</t>
+          <t>99927178-512e-41d2-8d22-79c20f037898</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-09 10:59:30</t>
+          <t>2026-08-09 11:07:34</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>726c3401-6186-492a-bcc8-0b71432b99cd</t>
+          <t>0a421413-31a7-403c-a3db-0e8a74189a00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>f70a76fc-46ed-4d6d-af60-e55ff79d976c</t>
+          <t>4e0a2487-0009-4c74-b6a7-9c4bda02f031</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -893,7 +893,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>67291ef5-7932-494a-a5ad-ea8ee894819d</t>
+          <t>bf44b90a-798f-45c7-8da0-077853bae445</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -939,7 +939,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>325043fb-6bec-4295-98c6-22e9e7559352</t>
+          <t>6afbb9d3-c2d4-4734-b29a-e19e2c7ec654</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1069,7 +1069,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>42a58560-9281-4d6b-a620-cf5960faee91</t>
+          <t>4099a030-a56a-498e-88e3-b8e033e16ccd</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1116,7 +1116,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3525d5ac-2903-44b3-9e6d-9175f626f2bb</t>
+          <t>0075db35-308d-4e7d-823c-09c96fb5dc9f</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1163,7 +1163,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>91efcd4b-44ac-42ae-970b-3a13d0524ea0</t>
+          <t>9dd60cca-e2f9-4fbf-b3c5-1e3edb1cde5e</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1210,7 +1210,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5c66bbba-eea9-4cfb-b61c-79ea2bf5b21d</t>
+          <t>0e2531b5-a16f-4482-910d-fddf737ed80d</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1257,7 +1257,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ea3dc646-aa67-4393-bb33-50a65c5c3cae</t>
+          <t>08bddfcc-b466-4cc0-b60c-1c167da5aed2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1304,7 +1304,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3996ba82-ef06-4fe6-acb1-bfbce8fdd71a</t>
+          <t>49417730-05de-441f-9791-6b8e872516c2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>d6c7d568-8465-4a05-ba87-58caa246cbc1</t>
+          <t>bdeefe75-5e6a-4a91-9bea-b579fec685c7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1398,7 +1398,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>fdf8c65c-11b0-4fcf-b0fd-621d5de4dd1b</t>
+          <t>22a63101-f161-4335-a699-7d2e388dfcb8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1505,7 +1505,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>c016901d-6f8b-4d51-998f-eeacff3b7301</t>
+          <t>852ae4ac-e667-4530-b8fc-8261da7f487b</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1531,14 +1531,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-09 10:59:30</t>
+          <t>2026-08-09 11:07:34</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>04719a7d-c411-4604-9577-c7410165aab0</t>
+          <t>247b1cf4-2916-4f9d-b639-66d96a027dca</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-08 10:59:30</t>
+          <t>2026-08-08 11:07:34</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>afa17b87-234f-4ec9-9438-45eeb63f1673</t>
+          <t>180d42ed-64cc-4ba7-9af6-38c038582950</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1657,14 +1657,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-09 10:59:32</t>
+          <t>2026-08-09 11:07:36</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>e05fb65b-8b92-45fb-ad77-7298d65b7dab</t>
+          <t>5ec6af7b-c2ad-47b5-b09e-046a5355172f</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1690,14 +1690,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-09 10:59:30</t>
+          <t>2026-08-09 11:07:34</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>575d97b0-2f02-494e-9211-70ecb9b4ac19</t>
+          <t>85eb8ae6-6c2b-45eb-b2f1-900116dde9f2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1723,14 +1723,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-09 10:59:30</t>
+          <t>2026-08-09 11:07:34</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>d4fec113-500d-48f7-9698-37fc15a10d14</t>
+          <t>bd8c184e-e65a-4bd9-b2a4-2eeb5698c40a</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1756,14 +1756,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-09 10:59:30</t>
+          <t>2026-08-09 11:07:34</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>e72b45c6-e1f4-46be-a202-20bf8af72c6d</t>
+          <t>90447a1f-7c27-4bea-87ee-31cabfbb00b0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1789,14 +1789,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-09 10:59:30</t>
+          <t>2026-08-09 11:07:34</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>e200b324-a1d3-4fa0-bec8-1721248b01b0</t>
+          <t>409f549e-2547-4cd6-a98d-903317592fc7</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1822,14 +1822,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-09 10:59:30</t>
+          <t>2026-08-09 11:07:34</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>be6cccf2-4ca6-4053-b3d4-95a10c91b426</t>
+          <t>c783a7c2-0dcc-41d9-a99d-30af47b5c4c8</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1855,14 +1855,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-09 10:59:30</t>
+          <t>2026-08-09 11:07:34</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3428dada-ec75-4021-8277-06dad01422b6</t>
+          <t>328ecf83-0a9a-4f1b-84d9-5247bdc89dd9</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1888,14 +1888,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-09 10:59:30</t>
+          <t>2026-08-09 11:07:34</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6ac26069-87a8-43f5-a411-2ccd1c4d73fe</t>
+          <t>9f0b0a96-d499-446c-8449-f327ecd209a4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1921,14 +1921,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-09 10:59:30</t>
+          <t>2026-08-09 11:07:34</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>c73e3b39-c516-49e0-b2f9-fd48f4ed1aad</t>
+          <t>b972caa7-3fd1-4e22-b4ac-74d7ae76f68d</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1954,14 +1954,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-09 10:59:30</t>
+          <t>2026-08-09 11:07:34</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>b471ca3e-ddfe-4087-9eb9-88ffe7076ccf</t>
+          <t>639ae274-b0bf-482d-b11f-1f37608cce43</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-08-09 10:59:30</t>
+          <t>2026-08-09 11:07:34</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2048,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>b56da297-d12b-4a48-88c6-0b901580fdb8</t>
+          <t>b2c86b57-5688-4870-bf32-0a8a75be3138</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2080,7 +2080,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>fe49f774-d442-4b23-8d91-0b0787150553</t>
+          <t>29531835-4335-4b87-83dd-99242b781d2e</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2113,7 +2113,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3cf8ed84-cd4a-48c0-b02f-36861b514214</t>
+          <t>5bf7c5f8-87fd-4c55-b33f-a12b26faa14b</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2145,7 +2145,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>17ec79f0-20ae-4171-b5b5-8c715a64916c</t>
+          <t>daf2eb62-dc92-40ec-86d3-a1f589eaedd5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2177,7 +2177,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>e746dbac-a6cf-45a5-9d3b-9495389b55e5</t>
+          <t>e37aeb2f-be8f-4f01-97d9-86decfd0800e</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2210,7 +2210,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>128e867e-8871-4205-80fd-09f89c27e8da</t>
+          <t>55e752ef-413a-41e9-b3f8-02433e0de037</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2243,7 +2243,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>b835b6b9-e51b-422c-a734-0d56ac44b4c7</t>
+          <t>ada9c6b2-9660-402d-8d20-d7e14196dbb7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2341,7 +2341,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>34717c3d-e914-43fe-a6d9-375f5b5d44a4</t>
+          <t>fa442b28-345d-4e2f-97a0-0d4b68ea1df2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2377,7 +2377,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>37beccf3-d8ab-429e-a5f7-df6fd048c9f6</t>
+          <t>6c95e23d-500a-467f-b889-ef12278dbc03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2473,7 +2473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5ff8ee9a-98bb-449d-ac77-1427d6c4721e</t>
+          <t>556d5835-a049-47ac-bcf7-d25951719a23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-09 10:59:30</t>
+          <t>2026-08-09 11:07:34</t>
         </is>
       </c>
     </row>

--- a/edufeedia_database_records.xlsx
+++ b/edufeedia_database_records.xlsx
@@ -501,7 +501,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>a6f7ba00-78db-48eb-b5b1-38cd17d66f41</t>
+          <t>c3b38c0c-9b37-4df9-8639-5f9c9f5c894d</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-09 11:07:32</t>
+          <t>2026-08-11 08:51:03</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0a421413-31a7-403c-a3db-0e8a74189a00</t>
+          <t>7a151494-44dc-4c89-938a-926e5d1ab694</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -568,14 +568,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-09 11:07:34</t>
+          <t>2026-08-11 08:51:04</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4e0a2487-0009-4c74-b6a7-9c4bda02f031</t>
+          <t>57a43490-601f-4694-9d22-e4fd11d03473</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -605,14 +605,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-09 11:07:34</t>
+          <t>2026-08-11 08:51:04</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>bf44b90a-798f-45c7-8da0-077853bae445</t>
+          <t>1d700017-8c65-4419-a809-d4807cc49bfd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -642,14 +642,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-09 11:07:34</t>
+          <t>2026-08-11 08:51:04</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6afbb9d3-c2d4-4734-b29a-e19e2c7ec654</t>
+          <t>9f06fa58-2eb4-4ac9-b50a-580cab3ebbfe</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -679,14 +679,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-09 11:07:34</t>
+          <t>2026-08-11 08:51:04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>99927178-512e-41d2-8d22-79c20f037898</t>
+          <t>e85516cb-ae0b-4531-a295-08ae63937c02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-09 11:07:34</t>
+          <t>2026-08-11 08:51:05</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0a421413-31a7-403c-a3db-0e8a74189a00</t>
+          <t>7a151494-44dc-4c89-938a-926e5d1ab694</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4e0a2487-0009-4c74-b6a7-9c4bda02f031</t>
+          <t>57a43490-601f-4694-9d22-e4fd11d03473</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -893,7 +893,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bf44b90a-798f-45c7-8da0-077853bae445</t>
+          <t>1d700017-8c65-4419-a809-d4807cc49bfd</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -939,7 +939,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6afbb9d3-c2d4-4734-b29a-e19e2c7ec654</t>
+          <t>9f06fa58-2eb4-4ac9-b50a-580cab3ebbfe</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1069,7 +1069,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4099a030-a56a-498e-88e3-b8e033e16ccd</t>
+          <t>86c8e2b9-eefc-462e-bc8b-f64a5f1e66ed</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1116,7 +1116,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0075db35-308d-4e7d-823c-09c96fb5dc9f</t>
+          <t>290b3e38-da2c-49ba-9643-089f90c10017</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1163,7 +1163,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9dd60cca-e2f9-4fbf-b3c5-1e3edb1cde5e</t>
+          <t>97b12010-f723-4fbf-af6d-d568519078d4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1210,7 +1210,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0e2531b5-a16f-4482-910d-fddf737ed80d</t>
+          <t>92b97854-2ca9-454e-b98c-f260ed66f29e</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1257,7 +1257,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08bddfcc-b466-4cc0-b60c-1c167da5aed2</t>
+          <t>ffb5256e-d791-4e79-acde-698d6764a7fc</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1304,7 +1304,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>49417730-05de-441f-9791-6b8e872516c2</t>
+          <t>48eb74d1-c44e-4aef-9bad-9dac897f542a</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>bdeefe75-5e6a-4a91-9bea-b579fec685c7</t>
+          <t>fc44404e-9dcb-4580-8966-bca0007c4a42</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1398,7 +1398,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>22a63101-f161-4335-a699-7d2e388dfcb8</t>
+          <t>27d2213a-c37b-44b3-80ea-e6d56dcb8cfc</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1505,7 +1505,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>852ae4ac-e667-4530-b8fc-8261da7f487b</t>
+          <t>6a0ee0ff-c945-4275-b4f8-e39621f5db71</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1531,14 +1531,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-09 11:07:34</t>
+          <t>2026-08-11 08:51:05</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>247b1cf4-2916-4f9d-b639-66d96a027dca</t>
+          <t>474156e2-81f9-4be9-a22c-2581c5c652eb</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-08 11:07:34</t>
+          <t>2026-08-10 08:51:05</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>180d42ed-64cc-4ba7-9af6-38c038582950</t>
+          <t>d32e54d9-c338-4324-80b1-9e9f8ce350e7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1657,14 +1657,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-09 11:07:36</t>
+          <t>2026-08-11 08:51:07</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5ec6af7b-c2ad-47b5-b09e-046a5355172f</t>
+          <t>d2e9a782-59e6-4cba-81c2-dab629c0894a</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1690,14 +1690,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-09 11:07:34</t>
+          <t>2026-08-11 08:51:05</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>85eb8ae6-6c2b-45eb-b2f1-900116dde9f2</t>
+          <t>14d0b27b-f0ca-4489-8a1e-93b253190944</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1723,14 +1723,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-09 11:07:34</t>
+          <t>2026-08-11 08:51:05</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>bd8c184e-e65a-4bd9-b2a4-2eeb5698c40a</t>
+          <t>d85f8d2e-6809-4d40-8d31-72d32e9dff65</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1756,14 +1756,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-09 11:07:34</t>
+          <t>2026-08-11 08:51:05</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>90447a1f-7c27-4bea-87ee-31cabfbb00b0</t>
+          <t>66258993-296b-4455-9f61-060b2faa9d60</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1789,14 +1789,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-09 11:07:34</t>
+          <t>2026-08-11 08:51:05</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>409f549e-2547-4cd6-a98d-903317592fc7</t>
+          <t>5e4d21fb-5c21-4093-afc6-15c7a711e4fc</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1822,14 +1822,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-09 11:07:34</t>
+          <t>2026-08-11 08:51:05</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>c783a7c2-0dcc-41d9-a99d-30af47b5c4c8</t>
+          <t>426af99e-3c69-4e14-8d03-365a99cf76d4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1855,14 +1855,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-09 11:07:34</t>
+          <t>2026-08-11 08:51:05</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>328ecf83-0a9a-4f1b-84d9-5247bdc89dd9</t>
+          <t>e9c75e5b-c099-4c42-bd54-7817d79a4e4f</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1888,14 +1888,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-09 11:07:34</t>
+          <t>2026-08-11 08:51:05</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9f0b0a96-d499-446c-8449-f327ecd209a4</t>
+          <t>7d1b2658-e63c-403c-bfd6-04191bde02c3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1921,14 +1921,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-09 11:07:34</t>
+          <t>2026-08-11 08:51:05</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>b972caa7-3fd1-4e22-b4ac-74d7ae76f68d</t>
+          <t>40503143-ed73-41e4-a39c-bb994c73975a</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1954,14 +1954,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-09 11:07:34</t>
+          <t>2026-08-11 08:51:05</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>639ae274-b0bf-482d-b11f-1f37608cce43</t>
+          <t>b902e8bc-367d-4b4c-8f1b-f14fa05cf44a</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-08-09 11:07:34</t>
+          <t>2026-08-11 08:51:05</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2048,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>b2c86b57-5688-4870-bf32-0a8a75be3138</t>
+          <t>d55ef681-4b3c-4439-9ea4-999709c07f19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2080,7 +2080,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>29531835-4335-4b87-83dd-99242b781d2e</t>
+          <t>b0813063-4c7c-4d42-a735-47a6e2c199b5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2113,7 +2113,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5bf7c5f8-87fd-4c55-b33f-a12b26faa14b</t>
+          <t>147a31a6-0559-41de-bb25-904aee880cdc</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2145,7 +2145,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>daf2eb62-dc92-40ec-86d3-a1f589eaedd5</t>
+          <t>63241b94-dd81-4610-b9b9-f1437c3acde8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2177,7 +2177,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>e37aeb2f-be8f-4f01-97d9-86decfd0800e</t>
+          <t>3b1122d7-cfe5-44a1-8827-731261d7028a</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2210,7 +2210,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>55e752ef-413a-41e9-b3f8-02433e0de037</t>
+          <t>83b5f8f8-3f1a-4b70-b7c3-3ef64ec4c236</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2243,7 +2243,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ada9c6b2-9660-402d-8d20-d7e14196dbb7</t>
+          <t>6c20908b-157c-414a-8dc6-bf252850addc</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2341,7 +2341,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>fa442b28-345d-4e2f-97a0-0d4b68ea1df2</t>
+          <t>989a535b-5951-49ae-9979-bcf5e6f63f87</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2370,14 +2370,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6c95e23d-500a-467f-b889-ef12278dbc03</t>
+          <t>61038520-32ab-4117-895b-182571684cff</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>556d5835-a049-47ac-bcf7-d25951719a23</t>
+          <t>a86c959b-9a66-40ee-a99e-82718819068d</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-09 11:07:34</t>
+          <t>2026-08-11 08:51:05</t>
         </is>
       </c>
     </row>

--- a/edufeedia_database_records.xlsx
+++ b/edufeedia_database_records.xlsx
@@ -501,7 +501,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>c3b38c0c-9b37-4df9-8639-5f9c9f5c894d</t>
+          <t>9c74e095-7cd6-42e1-a1a2-a4c6af8994df</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-11 08:51:03</t>
+          <t>2026-08-11 09:24:47</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>7a151494-44dc-4c89-938a-926e5d1ab694</t>
+          <t>5188ffbb-8492-47c9-a181-39530495f979</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -568,14 +568,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-11 08:51:04</t>
+          <t>2026-08-11 09:24:48</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>57a43490-601f-4694-9d22-e4fd11d03473</t>
+          <t>179a88b9-8a8a-4d8e-8db2-729f6d01f58e</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -605,14 +605,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-11 08:51:04</t>
+          <t>2026-08-11 09:24:48</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1d700017-8c65-4419-a809-d4807cc49bfd</t>
+          <t>ebd2c300-834e-4135-bc87-c84f52f7e4b5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -642,14 +642,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-11 08:51:04</t>
+          <t>2026-08-11 09:24:48</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9f06fa58-2eb4-4ac9-b50a-580cab3ebbfe</t>
+          <t>9814461c-1776-46ea-96fe-2978b856568a</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -679,14 +679,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-11 08:51:04</t>
+          <t>2026-08-11 09:24:48</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>e85516cb-ae0b-4531-a295-08ae63937c02</t>
+          <t>68984395-1e22-4210-89da-3c2144858b87</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-11 08:51:05</t>
+          <t>2026-08-11 09:24:49</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7a151494-44dc-4c89-938a-926e5d1ab694</t>
+          <t>5188ffbb-8492-47c9-a181-39530495f979</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>57a43490-601f-4694-9d22-e4fd11d03473</t>
+          <t>179a88b9-8a8a-4d8e-8db2-729f6d01f58e</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -893,7 +893,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1d700017-8c65-4419-a809-d4807cc49bfd</t>
+          <t>ebd2c300-834e-4135-bc87-c84f52f7e4b5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -939,7 +939,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9f06fa58-2eb4-4ac9-b50a-580cab3ebbfe</t>
+          <t>9814461c-1776-46ea-96fe-2978b856568a</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1069,7 +1069,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>86c8e2b9-eefc-462e-bc8b-f64a5f1e66ed</t>
+          <t>dc004d55-4f1f-4803-8422-c05b9782e2f1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1116,7 +1116,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>290b3e38-da2c-49ba-9643-089f90c10017</t>
+          <t>c7198ee0-ebd1-46fc-958b-f99d0c446f82</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1163,7 +1163,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>97b12010-f723-4fbf-af6d-d568519078d4</t>
+          <t>bd79b6b3-950e-40dc-97bc-04e550b7e62c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1210,7 +1210,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>92b97854-2ca9-454e-b98c-f260ed66f29e</t>
+          <t>4f6c7683-3e52-48ff-b8b4-d9dff51cef50</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I5" t="n">
         <v>97</v>
@@ -1257,7 +1257,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ffb5256e-d791-4e79-acde-698d6764a7fc</t>
+          <t>990a8afc-92cb-48ad-a199-42380c8dbca5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I6" t="n">
         <v>94</v>
@@ -1304,7 +1304,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>48eb74d1-c44e-4aef-9bad-9dac897f542a</t>
+          <t>a5f2a297-15cc-448f-9881-cf85006ae2b2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>fc44404e-9dcb-4580-8966-bca0007c4a42</t>
+          <t>972f6e5c-e6a0-4c56-9bd1-0c340780c7c7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1398,7 +1398,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>27d2213a-c37b-44b3-80ea-e6d56dcb8cfc</t>
+          <t>934d32ed-1aab-415c-89d6-358be879d654</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1505,7 +1505,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6a0ee0ff-c945-4275-b4f8-e39621f5db71</t>
+          <t>eeada175-fca8-49c4-b1fd-b0ee6c33e38d</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1531,14 +1531,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-11 08:51:05</t>
+          <t>2026-08-11 09:24:49</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>474156e2-81f9-4be9-a22c-2581c5c652eb</t>
+          <t>91325aa8-3884-4c4f-879d-fe9f7d580e0e</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-10 08:51:05</t>
+          <t>2026-08-10 09:24:49</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d32e54d9-c338-4324-80b1-9e9f8ce350e7</t>
+          <t>a3ea2518-586f-495f-8c4e-ee62f5e0c37d</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1657,14 +1657,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-11 08:51:07</t>
+          <t>2026-08-11 09:24:50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>d2e9a782-59e6-4cba-81c2-dab629c0894a</t>
+          <t>896444df-f64d-496d-b983-cc4643811c87</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1690,14 +1690,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-11 08:51:05</t>
+          <t>2026-08-11 09:24:49</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>14d0b27b-f0ca-4489-8a1e-93b253190944</t>
+          <t>3a9d29a3-feea-4ce1-9719-cb4f0a593387</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1723,14 +1723,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-11 08:51:05</t>
+          <t>2026-08-11 09:24:49</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>d85f8d2e-6809-4d40-8d31-72d32e9dff65</t>
+          <t>0e7d27b5-61e6-42e0-b3f2-47a2e85eb521</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1756,14 +1756,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-11 08:51:05</t>
+          <t>2026-08-11 09:24:49</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>66258993-296b-4455-9f61-060b2faa9d60</t>
+          <t>a5c9d946-c777-4ab0-9739-5a65154f294b</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1789,14 +1789,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-11 08:51:05</t>
+          <t>2026-08-11 09:24:49</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5e4d21fb-5c21-4093-afc6-15c7a711e4fc</t>
+          <t>f76564f5-a886-4ee3-8622-b8114c09cda0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1822,14 +1822,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-11 08:51:05</t>
+          <t>2026-08-11 09:24:49</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>426af99e-3c69-4e14-8d03-365a99cf76d4</t>
+          <t>77380076-39c0-4deb-b4d5-cfb688781421</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1855,14 +1855,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-11 08:51:05</t>
+          <t>2026-08-11 09:24:49</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>e9c75e5b-c099-4c42-bd54-7817d79a4e4f</t>
+          <t>37210ae1-299b-4cca-822f-4acd23b47139</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1888,14 +1888,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-11 08:51:05</t>
+          <t>2026-08-11 09:24:49</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>7d1b2658-e63c-403c-bfd6-04191bde02c3</t>
+          <t>fca5d5c0-e01e-44fc-a9fa-8daff4cfd669</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1921,14 +1921,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-11 08:51:05</t>
+          <t>2026-08-11 09:24:49</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>40503143-ed73-41e4-a39c-bb994c73975a</t>
+          <t>60f47fc6-0c3f-4ef1-8a3b-4463ab10d445</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1954,14 +1954,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-11 08:51:05</t>
+          <t>2026-08-11 09:24:49</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>b902e8bc-367d-4b4c-8f1b-f14fa05cf44a</t>
+          <t>f2dfd205-6546-4195-bb6a-6ca7a0b12291</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-08-11 08:51:05</t>
+          <t>2026-08-11 09:24:49</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2048,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d55ef681-4b3c-4439-9ea4-999709c07f19</t>
+          <t>5a069d61-b1e4-4cb0-9f4f-82cd4deed676</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2080,7 +2080,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>b0813063-4c7c-4d42-a735-47a6e2c199b5</t>
+          <t>9a21e9f2-94ef-4281-939c-9df59fe61c66</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2113,7 +2113,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>147a31a6-0559-41de-bb25-904aee880cdc</t>
+          <t>78c9ad86-5756-4e5c-861c-d3881ee387c4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2145,7 +2145,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>63241b94-dd81-4610-b9b9-f1437c3acde8</t>
+          <t>16263969-4b88-4783-b28c-46655d535933</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2177,7 +2177,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3b1122d7-cfe5-44a1-8827-731261d7028a</t>
+          <t>12659737-486a-412b-a93d-3369b17f15fd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2210,7 +2210,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>83b5f8f8-3f1a-4b70-b7c3-3ef64ec4c236</t>
+          <t>28ab1827-c4fd-4cea-9904-31ec86f09fb2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2243,7 +2243,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6c20908b-157c-414a-8dc6-bf252850addc</t>
+          <t>aea52dff-1b7c-497b-bf60-660723eb94a7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2341,7 +2341,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>989a535b-5951-49ae-9979-bcf5e6f63f87</t>
+          <t>07785d3a-bfc0-40cb-af9e-7b275f996c8f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2377,7 +2377,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>61038520-32ab-4117-895b-182571684cff</t>
+          <t>b0b9b75c-1c27-4793-973a-2581576894b3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2473,7 +2473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>a86c959b-9a66-40ee-a99e-82718819068d</t>
+          <t>5971218c-b082-4165-a4e7-f66224527289</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-11 08:51:05</t>
+          <t>2026-08-11 09:24:49</t>
         </is>
       </c>
     </row>
